--- a/research/traditional_assets/database/data/tunisia/tunisia_information_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_information_services.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0151</v>
+        <v>0.0346</v>
+      </c>
+      <c r="E2">
+        <v>0.09570000000000001</v>
       </c>
       <c r="G2">
-        <v>0.190566037735849</v>
+        <v>0.2464705882352941</v>
       </c>
       <c r="H2">
-        <v>0.190566037735849</v>
+        <v>0.2464705882352941</v>
       </c>
       <c r="I2">
-        <v>0.1886792452830189</v>
+        <v>0.2317647058823529</v>
       </c>
       <c r="J2">
-        <v>0.1614124327201751</v>
+        <v>0.1993802861685214</v>
       </c>
       <c r="K2">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>0.1685534591194969</v>
+        <v>0.1852941176470588</v>
       </c>
       <c r="M2">
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>0.02457865168539326</v>
+        <v>0.1</v>
       </c>
       <c r="O2">
-        <v>0.3264925373134328</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="P2">
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="Q2">
-        <v>0.02457865168539326</v>
+        <v>0.1</v>
       </c>
       <c r="R2">
-        <v>0.3264925373134328</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.73</v>
+        <v>4.44</v>
       </c>
       <c r="V2">
-        <v>0.1047752808988764</v>
+        <v>0.148</v>
       </c>
       <c r="W2">
-        <v>0.2653465346534654</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="X2">
-        <v>0.1563510132711007</v>
+        <v>0.2945628449748224</v>
       </c>
       <c r="Y2">
-        <v>0.1089955213823647</v>
+        <v>-0.02533207574405316</v>
       </c>
       <c r="Z2">
-        <v>3.896103896103897</v>
+        <v>2.139441228290965</v>
       </c>
       <c r="AA2">
-        <v>0.6288796080006821</v>
+        <v>0.4265624043373856</v>
       </c>
       <c r="AB2">
-        <v>0.1555272336456218</v>
+        <v>0.2926783889521212</v>
       </c>
       <c r="AC2">
-        <v>0.4733523743550603</v>
+        <v>0.1338840153852644</v>
       </c>
       <c r="AD2">
-        <v>0.36</v>
+        <v>0.324</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.36</v>
+        <v>0.324</v>
       </c>
       <c r="AG2">
-        <v>-3.37</v>
+        <v>-4.116000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0100111234705228</v>
+        <v>0.01068460625247329</v>
       </c>
       <c r="AI2">
-        <v>0.02960526315789474</v>
+        <v>0.02740189445196211</v>
       </c>
       <c r="AJ2">
-        <v>-0.1045609680421967</v>
+        <v>-0.1590171534538711</v>
       </c>
       <c r="AK2">
-        <v>-0.3997627520759194</v>
+        <v>-0.5574214517876491</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.008999999999999999</v>
+        <v>-0.025</v>
       </c>
       <c r="AN2">
-        <v>0.1090909090909091</v>
+        <v>0.07695961995249406</v>
       </c>
       <c r="AP2">
-        <v>-1.021212121212121</v>
+        <v>-0.9776722090261284</v>
       </c>
       <c r="AQ2">
-        <v>-333.3333333333334</v>
+        <v>-157.6</v>
       </c>
     </row>
     <row r="3">
@@ -716,43 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0151</v>
+        <v>0.0346</v>
+      </c>
+      <c r="E3">
+        <v>0.09570000000000001</v>
       </c>
       <c r="G3">
-        <v>0.190566037735849</v>
+        <v>0.2464705882352941</v>
       </c>
       <c r="H3">
-        <v>0.190566037735849</v>
+        <v>0.2464705882352941</v>
       </c>
       <c r="I3">
-        <v>0.1886792452830189</v>
+        <v>0.2317647058823529</v>
       </c>
       <c r="J3">
-        <v>0.1614124327201751</v>
+        <v>0.1993802861685214</v>
       </c>
       <c r="K3">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
-        <v>0.1685534591194969</v>
+        <v>0.1852941176470588</v>
       </c>
       <c r="M3">
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="N3">
-        <v>0.02457865168539326</v>
+        <v>0.1</v>
       </c>
       <c r="O3">
-        <v>0.3264925373134328</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="P3">
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>0.02457865168539326</v>
+        <v>0.1</v>
       </c>
       <c r="R3">
-        <v>0.3264925373134328</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.73</v>
+        <v>4.44</v>
       </c>
       <c r="V3">
-        <v>0.1047752808988764</v>
+        <v>0.148</v>
       </c>
       <c r="W3">
-        <v>0.2653465346534654</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="X3">
-        <v>0.1563510132711007</v>
+        <v>0.2945628449748224</v>
       </c>
       <c r="Y3">
-        <v>0.1089955213823647</v>
+        <v>-0.02533207574405316</v>
       </c>
       <c r="Z3">
-        <v>3.896103896103897</v>
+        <v>2.139441228290965</v>
       </c>
       <c r="AA3">
-        <v>0.6288796080006821</v>
+        <v>0.4265624043373856</v>
       </c>
       <c r="AB3">
-        <v>0.1555272336456218</v>
+        <v>0.2926783889521212</v>
       </c>
       <c r="AC3">
-        <v>0.4733523743550603</v>
+        <v>0.1338840153852644</v>
       </c>
       <c r="AD3">
-        <v>0.36</v>
+        <v>0.324</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.36</v>
+        <v>0.324</v>
       </c>
       <c r="AG3">
-        <v>-3.37</v>
+        <v>-4.116000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0100111234705228</v>
+        <v>0.01068460625247329</v>
       </c>
       <c r="AI3">
-        <v>0.02960526315789474</v>
+        <v>0.02740189445196211</v>
       </c>
       <c r="AJ3">
-        <v>-0.1045609680421967</v>
+        <v>-0.1590171534538711</v>
       </c>
       <c r="AK3">
-        <v>-0.3997627520759194</v>
+        <v>-0.5574214517876491</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.008999999999999999</v>
+        <v>-0.025</v>
       </c>
       <c r="AN3">
-        <v>0.1090909090909091</v>
+        <v>0.07695961995249406</v>
       </c>
       <c r="AP3">
-        <v>-1.021212121212121</v>
+        <v>-0.9776722090261284</v>
       </c>
       <c r="AQ3">
-        <v>-333.3333333333334</v>
+        <v>-157.6</v>
       </c>
     </row>
   </sheetData>
